--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3B2F0E-4319-4165-8E78-CE2AE49AC65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70294B4D-FB7C-4D51-821A-A729B6D20ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -8776,7 +8776,7 @@
         <v>584</v>
       </c>
       <c r="C2" s="2">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="D2" s="2">
         <v>46278</v>
